--- a/reports/集团总公司_现金流量表_2025-12.xlsx
+++ b/reports/集团总公司_现金流量表_2025-12.xlsx
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>189150000</v>
+        <v>190034414</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>2359500000</v>
+        <v>2358834614</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2015,10 +2015,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>3869493</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>48521774</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>1953786</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>24252593</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>968253</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>12128125</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>780087</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>9703045</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>582452</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>7275410</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>388861</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>4852369</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>292157</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>3637234</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>193845</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>2426354</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2239,10 +2239,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>488147</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>6062032</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>243122</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>3048306</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>155331</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>1927654</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2323,10 +2323,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>514100</v>
+        <v>511726</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>6413000</v>
+        <v>6413603</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>3492000</v>
+        <v>3505145</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>43560000</v>
+        <v>43560446</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>193156100</v>
+        <v>203966819</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>116400000</v>
+        <v>116805772</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>1452000000</v>
+        <v>1451529363</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2505,10 +2505,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>1290543</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>16175266</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2533,10 +2533,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>977038</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>12124900</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>644963</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>8086507</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2589,10 +2589,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>488249</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>6063548</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>322977</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>4042429</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2645,10 +2645,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>244803</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>3047946</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>23474000</v>
+        <v>23462672</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>292820000</v>
+        <v>292752518</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>10864000</v>
+        <v>10851715</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>135520000</v>
+        <v>135559527</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>4947000</v>
+        <v>4959991</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>61710000</v>
+        <v>61690107</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>155685000</v>
+        <v>160048723</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>37471100</v>
+        <v>43918096</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -2913,10 +2913,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>240000</v>
+        <v>239628</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>2880000</v>
+        <v>2879492</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>2100000</v>
+        <v>2103444</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>25200000</v>
+        <v>25192202</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>1280000</v>
+        <v>1276081</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>15360000</v>
+        <v>15365081</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>2340000</v>
+        <v>2343072</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>20000000</v>
+        <v>19903417</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>240000000</v>
+        <v>240064908</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>2900000</v>
+        <v>2914471</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>34800000</v>
+        <v>34793194</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3107,10 +3107,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>14200000</v>
+        <v>14134261</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>170400000</v>
+        <v>170417072</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3219,10 +3219,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>520000</v>
+        <v>520300</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>6240000</v>
+        <v>6238272</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3247,7 +3247,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>20520000</v>
+        <v>20423717</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-18180000</v>
+        <v>-18080645</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3323,10 +3323,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>4700000</v>
+        <v>4723215</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>56400000</v>
+        <v>56385976</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3379,10 +3379,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>7500000</v>
+        <v>7533024</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>90000000</v>
+        <v>89994040</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3407,10 +3407,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>7500000</v>
+        <v>7474372</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>90000000</v>
+        <v>89996338</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>240000</v>
+        <v>240497</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>2880000</v>
+        <v>2880413</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>12440000</v>
+        <v>12496736</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>6100000</v>
+        <v>6093287</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>73200000</v>
+        <v>73221552</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>6100000</v>
+        <v>6115856</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>73200000</v>
+        <v>73176056</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>1000000</v>
+        <v>996174</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>12000000</v>
+        <v>12003907</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3597,10 +3597,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>870000</v>
+        <v>865655</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>10440000</v>
+        <v>10442340</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>125000</v>
+        <v>125601</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>1500000</v>
+        <v>1499800</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>7225000</v>
+        <v>7215062</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>5215000</v>
+        <v>5281674</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -3729,7 +3729,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>24506100</v>
+        <v>31119125</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>24506100</v>
+        <v>31119125</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
